--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0001T0006Z000C1N99_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0001T0006Z000C1N99_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>28.57939571974654</v>
+        <v>4.644151804458813</v>
       </c>
       <c r="D2" t="n">
-        <v>29.32226791655103</v>
+        <v>4.764868536439543</v>
       </c>
       <c r="E2" t="n">
-        <v>12.04108652592406</v>
+        <v>1.95667656046266</v>
       </c>
       <c r="F2" t="n">
-        <v>12.40562732038723</v>
+        <v>2.015914439562925</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>43.89584977184541</v>
+        <v>7.133075587924878</v>
       </c>
       <c r="D3" t="n">
-        <v>45.30091766766257</v>
+        <v>7.361399120995168</v>
       </c>
       <c r="E3" t="n">
-        <v>12.04108652592406</v>
+        <v>1.95667656046266</v>
       </c>
       <c r="F3" t="n">
-        <v>12.40562732038723</v>
+        <v>2.015914439562925</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>19.43892107012236</v>
+        <v>3.158824673894884</v>
       </c>
       <c r="D4" t="n">
-        <v>18.8858949578015</v>
+        <v>3.068957930642744</v>
       </c>
       <c r="E4" t="n">
-        <v>12.04108652592406</v>
+        <v>1.95667656046266</v>
       </c>
       <c r="F4" t="n">
-        <v>12.40562732038723</v>
+        <v>2.015914439562925</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>8.473200784871398</v>
+        <v>1.376895127541602</v>
       </c>
       <c r="D5" t="n">
-        <v>9.184818736093399</v>
+        <v>1.492533044615177</v>
       </c>
       <c r="E5" t="n">
-        <v>12.04108652592406</v>
+        <v>1.95667656046266</v>
       </c>
       <c r="F5" t="n">
-        <v>12.40562732038723</v>
+        <v>2.015914439562925</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>17.10853526476777</v>
+        <v>2.780136980524763</v>
       </c>
       <c r="D6" t="n">
-        <v>17.5340090490574</v>
+        <v>2.849276470471828</v>
       </c>
       <c r="E6" t="n">
-        <v>12.04108652592406</v>
+        <v>1.95667656046266</v>
       </c>
       <c r="F6" t="n">
-        <v>12.40562732038723</v>
+        <v>2.015914439562925</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
